--- a/survey_templates/044_healthcare_employee_satisfaction_survey--survey_templates.xlsx
+++ b/survey_templates/044_healthcare_employee_satisfaction_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>patient_care_team_skills</t>
+          <t>patient_care_team_skills_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How would you rate the staff care team's skills?</t>
+          <t>Patient Care Team Skills 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>staff_communication</t>
+          <t>staff_communication_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What do you think about communication with your team?</t>
+          <t>Staff Communication 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>staff_communication</t>
+          <t>staff_communication_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What do you think about communication with your team?</t>
+          <t>Staff Communication 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>staff_communication</t>
+          <t>staff_communication_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Is there a way to improve communication with staff?</t>
+          <t>Feedback 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>patient_care_team_skills_choices</t>
+          <t>patient_care_team_skills_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1472,7 +1472,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>patient_care_team_skills_choices</t>
+          <t>patient_care_team_skills_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>staff_communication_choices</t>
+          <t>staff_communication_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>staff_communication_choices</t>
+          <t>staff_communication_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>staff_communication_choices</t>
+          <t>staff_communication_3_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>staff_communication_choices</t>
+          <t>staff_communication_3_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>staff_communication_choices</t>
+          <t>staff_communication_4_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1642,7 +1642,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>staff_communication_choices</t>
+          <t>staff_communication_4_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1693,7 +1693,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1710,7 +1710,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1744,7 +1744,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_4_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>feedback_4_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
